--- a/exports/trend_1d/BHARATFORG_full_report.xlsx
+++ b/exports/trend_1d/BHARATFORG_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="H2" t="n">
-        <v>650.25</v>
+        <v>598.58</v>
       </c>
       <c r="I2" t="n">
         <v>603.5339295250972</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K2" t="n">
-        <v>32.17</v>
+        <v>21.67</v>
       </c>
       <c r="L2" t="n">
         <v>1.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.99</v>
+        <v>1.35</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>7.95</v>
       </c>
       <c r="O2" t="n">
         <v>0.08</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>15.11</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42220</v>
+        <v>42221</v>
       </c>
       <c r="H3" t="n">
-        <v>588.55</v>
+        <v>621.8</v>
       </c>
       <c r="I3" t="n">
         <v>592.8514502064285</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K3" t="n">
-        <v>1.68</v>
+        <v>-3.88</v>
       </c>
       <c r="L3" t="n">
         <v>11.24</v>
@@ -612,7 +647,7 @@
         <v>1.92</v>
       </c>
       <c r="N3" t="n">
-        <v>4.85</v>
+        <v>5.65</v>
       </c>
       <c r="O3" t="n">
         <v>-7.95</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.2</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>609.9</v>
+        <v>558.95</v>
       </c>
       <c r="I4" t="n">
         <v>573.2190839720554</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.91</v>
+        <v>-10.11</v>
       </c>
       <c r="L4" t="n">
-        <v>7.47</v>
+        <v>12.67</v>
       </c>
       <c r="M4" t="n">
-        <v>1.71</v>
+        <v>5.72</v>
       </c>
       <c r="N4" t="n">
-        <v>3.23</v>
+        <v>8.35</v>
       </c>
       <c r="O4" t="n">
         <v>5.65</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.97</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42362</v>
+        <v>42366</v>
       </c>
       <c r="H5" t="n">
-        <v>430.13</v>
+        <v>452.35</v>
       </c>
       <c r="I5" t="n">
         <v>435.833639723955</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K5" t="n">
-        <v>23.05</v>
+        <v>19.07</v>
       </c>
       <c r="L5" t="n">
         <v>7.34</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.76</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H6" t="n">
-        <v>438.18</v>
+        <v>412.33</v>
       </c>
       <c r="I6" t="n">
         <v>413.4213295346549</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.13</v>
+        <v>-8.85</v>
       </c>
       <c r="L6" t="n">
-        <v>5.55</v>
+        <v>9.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14</v>
+        <v>0.73</v>
       </c>
       <c r="N6" t="n">
-        <v>1.89</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
         <v>5.17</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.52</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42446</v>
+        <v>42447</v>
       </c>
       <c r="H7" t="n">
-        <v>412.73</v>
+        <v>424.53</v>
       </c>
       <c r="I7" t="n">
         <v>418.3055138586498</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1</v>
+        <v>-2.96</v>
       </c>
       <c r="L7" t="n">
         <v>5.98</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.99</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42465</v>
+        <v>42466</v>
       </c>
       <c r="H8" t="n">
-        <v>415.1</v>
+        <v>394.08</v>
       </c>
       <c r="I8" t="n">
         <v>405.6374680773943</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.22</v>
+        <v>-7.17</v>
       </c>
       <c r="L8" t="n">
-        <v>3.18</v>
+        <v>7.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.55</v>
+        <v>3.64</v>
       </c>
       <c r="N8" t="n">
-        <v>1.98</v>
+        <v>5.06</v>
       </c>
       <c r="O8" t="n">
         <v>2.86</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.71</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42586</v>
+        <v>42587</v>
       </c>
       <c r="H9" t="n">
-        <v>362.23</v>
+        <v>407.15</v>
       </c>
       <c r="I9" t="n">
         <v>389.9191923041009</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K9" t="n">
-        <v>8.08</v>
+        <v>-3.32</v>
       </c>
       <c r="L9" t="n">
         <v>6.64</v>
@@ -954,7 +1061,7 @@
         <v>1.94</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>12.4</v>
       </c>
       <c r="O9" t="n">
         <v>-5.06</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>15.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42668</v>
+        <v>42669</v>
       </c>
       <c r="H10" t="n">
-        <v>438.15</v>
+        <v>435.93</v>
       </c>
       <c r="I10" t="n">
         <v>437.3799769425104</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K10" t="n">
-        <v>7.61</v>
+        <v>7.07</v>
       </c>
       <c r="L10" t="n">
         <v>11.69</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42697</v>
+        <v>42698</v>
       </c>
       <c r="H11" t="n">
-        <v>448.95</v>
+        <v>456.88</v>
       </c>
       <c r="I11" t="n">
         <v>456.6521234839519</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.99</v>
+        <v>-4.81</v>
       </c>
       <c r="L11" t="n">
         <v>5.98</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.09</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H12" t="n">
-        <v>455.98</v>
+        <v>440.75</v>
       </c>
       <c r="I12" t="n">
         <v>444.0402584633495</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2</v>
+        <v>-3.53</v>
       </c>
       <c r="L12" t="n">
         <v>5.84</v>
@@ -1125,7 +1268,7 @@
         <v>1.98</v>
       </c>
       <c r="N12" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="O12" t="n">
         <v>1.77</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>11.7</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42769</v>
+        <v>42772</v>
       </c>
       <c r="H13" t="n">
-        <v>474.4</v>
+        <v>494.58</v>
       </c>
       <c r="I13" t="n">
         <v>492.3062173161531</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.63</v>
+        <v>-12.21</v>
       </c>
       <c r="L13" t="n">
-        <v>11.74</v>
+        <v>12.54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.37</v>
+        <v>2.24</v>
       </c>
       <c r="N13" t="n">
         <v>4.37</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>8.9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42872</v>
+        <v>42873</v>
       </c>
       <c r="H14" t="n">
-        <v>562.1</v>
+        <v>528.23</v>
       </c>
       <c r="I14" t="n">
         <v>530.2749759422019</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K14" t="n">
-        <v>13.65</v>
+        <v>6.8</v>
       </c>
       <c r="L14" t="n">
         <v>2.95</v>
       </c>
       <c r="M14" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.08</v>
+        <v>6.03</v>
       </c>
       <c r="O14" t="n">
         <v>4.25</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>11.95</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42885</v>
+        <v>42886</v>
       </c>
       <c r="H15" t="n">
-        <v>572.38</v>
+        <v>584.9299999999999</v>
       </c>
       <c r="I15" t="n">
         <v>574.3914868884309</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.359999999999999</v>
+        <v>-10.73</v>
       </c>
       <c r="L15" t="n">
-        <v>9.51</v>
+        <v>11.69</v>
       </c>
       <c r="M15" t="n">
         <v>1.44</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>10.09</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42909</v>
+        <v>42913</v>
       </c>
       <c r="H16" t="n">
-        <v>554.73</v>
+        <v>545.1</v>
       </c>
       <c r="I16" t="n">
         <v>549.4492094258781</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.16</v>
+        <v>-6.81</v>
       </c>
       <c r="L16" t="n">
-        <v>5.63</v>
+        <v>7.91</v>
       </c>
       <c r="M16" t="n">
         <v>1.23</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42954</v>
+        <v>42955</v>
       </c>
       <c r="H17" t="n">
-        <v>580.78</v>
+        <v>594.33</v>
       </c>
       <c r="I17" t="n">
         <v>584.5436024035019</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.55</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>7.76</v>
+        <v>9.93</v>
       </c>
       <c r="M17" t="n">
         <v>1.73</v>
       </c>
       <c r="N17" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="O17" t="n">
         <v>-1.74</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.74</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43006</v>
+        <v>43007</v>
       </c>
       <c r="H18" t="n">
-        <v>599.15</v>
+        <v>588.9</v>
       </c>
       <c r="I18" t="n">
         <v>591.3038266468579</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.91</v>
       </c>
       <c r="L18" t="n">
         <v>6.7</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>11.58</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H19" t="n">
-        <v>637.35</v>
+        <v>657.4</v>
       </c>
       <c r="I19" t="n">
         <v>657.0697458751704</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.23</v>
+        <v>-11.63</v>
       </c>
       <c r="L19" t="n">
-        <v>11.9</v>
+        <v>12.05</v>
       </c>
       <c r="M19" t="n">
         <v>1.88</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H20" t="n">
-        <v>724.45</v>
+        <v>690.8</v>
       </c>
       <c r="I20" t="n">
         <v>696.1703801664497</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>10.2</v>
+        <v>5.08</v>
       </c>
       <c r="L20" t="n">
         <v>3.89</v>
       </c>
       <c r="M20" t="n">
-        <v>0.84</v>
+        <v>1.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.38</v>
+        <v>4.64</v>
       </c>
       <c r="O20" t="n">
         <v>3.15</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>10.95</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43140</v>
+        <v>43143</v>
       </c>
       <c r="H21" t="n">
-        <v>762.8</v>
+        <v>776.35</v>
       </c>
       <c r="I21" t="n">
         <v>766.462761915275</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.42</v>
+        <v>-12.38</v>
       </c>
       <c r="L21" t="n">
-        <v>12.2</v>
+        <v>13.12</v>
       </c>
       <c r="M21" t="n">
         <v>1.59</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>11.16</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43175</v>
+        <v>43178</v>
       </c>
       <c r="H22" t="n">
-        <v>736.6</v>
+        <v>709.25</v>
       </c>
       <c r="I22" t="n">
         <v>715.631373986755</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.12</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>6.78</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>0.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.67</v>
+        <v>3.71</v>
       </c>
       <c r="O22" t="n">
         <v>1.78</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>10.83</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43208</v>
+        <v>43209</v>
       </c>
       <c r="H23" t="n">
-        <v>736.65</v>
+        <v>750.8</v>
       </c>
       <c r="I23" t="n">
         <v>750.0995738458449</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.86</v>
+        <v>-5.86</v>
       </c>
       <c r="L23" t="n">
-        <v>5.18</v>
+        <v>6.31</v>
       </c>
       <c r="M23" t="n">
         <v>1.61</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>6.8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43229</v>
+        <v>43230</v>
       </c>
       <c r="H24" t="n">
-        <v>728.95</v>
+        <v>724.25</v>
       </c>
       <c r="I24" t="n">
         <v>728.2495523315932</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.91</v>
+        <v>-3.54</v>
       </c>
       <c r="L24" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="M24" t="n">
         <v>1.14</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.86</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H25" t="n">
-        <v>640.85</v>
+        <v>652.25</v>
       </c>
       <c r="I25" t="n">
         <v>648.4060018733501</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K25" t="n">
-        <v>11.52</v>
+        <v>9.94</v>
       </c>
       <c r="L25" t="n">
         <v>3.68</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.36</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H26" t="n">
-        <v>624.55</v>
+        <v>608.05</v>
       </c>
       <c r="I26" t="n">
         <v>620.80070701974</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.25</v>
+        <v>-6.78</v>
       </c>
       <c r="L26" t="n">
         <v>8.65</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>14.29</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43522</v>
+        <v>43523</v>
       </c>
       <c r="H27" t="n">
-        <v>506.25</v>
+        <v>511.2</v>
       </c>
       <c r="I27" t="n">
         <v>506.9839753342352</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K27" t="n">
-        <v>16.74</v>
+        <v>15.93</v>
       </c>
       <c r="L27" t="n">
         <v>4.81</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43546</v>
+        <v>43549</v>
       </c>
       <c r="H28" t="n">
-        <v>494.6</v>
+        <v>487.6</v>
       </c>
       <c r="I28" t="n">
         <v>487.6394394956895</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.25</v>
+        <v>-4.62</v>
       </c>
       <c r="L28" t="n">
-        <v>3.76</v>
+        <v>5.71</v>
       </c>
       <c r="M28" t="n">
         <v>1.11</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43612</v>
+        <v>43613</v>
       </c>
       <c r="H29" t="n">
-        <v>482.35</v>
+        <v>489.75</v>
       </c>
       <c r="I29" t="n">
         <v>489.2544115039661</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K29" t="n">
-        <v>1.08</v>
+        <v>-0.44</v>
       </c>
       <c r="L29" t="n">
         <v>7.26</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>9.4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43630</v>
+        <v>43633</v>
       </c>
       <c r="H30" t="n">
-        <v>454.35</v>
+        <v>442.7</v>
       </c>
       <c r="I30" t="n">
         <v>443.7350460663287</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.23</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>7.71</v>
+        <v>10.06</v>
       </c>
       <c r="M30" t="n">
         <v>1.52</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>10.53</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43649</v>
+        <v>43650</v>
       </c>
       <c r="H31" t="n">
-        <v>462.75</v>
+        <v>475.95</v>
       </c>
       <c r="I31" t="n">
         <v>467.9397120142465</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.53</v>
+        <v>-7.51</v>
       </c>
       <c r="L31" t="n">
-        <v>7.05</v>
+        <v>8.83</v>
       </c>
       <c r="M31" t="n">
         <v>0.61</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.58</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43670</v>
+        <v>43671</v>
       </c>
       <c r="H32" t="n">
-        <v>431.55</v>
+        <v>428.25</v>
       </c>
       <c r="I32" t="n">
         <v>430.3508088766931</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.33</v>
+        <v>-10.02</v>
       </c>
       <c r="L32" t="n">
         <v>11.46</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>11.12</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H33" t="n">
-        <v>394.15</v>
+        <v>424.6</v>
       </c>
       <c r="I33" t="n">
         <v>420.3511922173793</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K33" t="n">
-        <v>7.96</v>
+        <v>0.85</v>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>4.62</v>
       </c>
       <c r="M33" t="n">
         <v>1.87</v>
       </c>
       <c r="N33" t="n">
-        <v>3.13</v>
+        <v>7.73</v>
       </c>
       <c r="O33" t="n">
         <v>-0.76</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.51</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H34" t="n">
-        <v>490.65</v>
+        <v>474.8</v>
       </c>
       <c r="I34" t="n">
         <v>487.6207724633584</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K34" t="n">
-        <v>15.56</v>
+        <v>11.82</v>
       </c>
       <c r="L34" t="n">
         <v>8.56</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H35" t="n">
-        <v>282.05</v>
+        <v>309.2</v>
       </c>
       <c r="I35" t="n">
         <v>296.9095085547074</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K35" t="n">
-        <v>40.6</v>
+        <v>34.88</v>
       </c>
       <c r="L35" t="n">
         <v>11.19</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>24.31</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44008</v>
+        <v>44011</v>
       </c>
       <c r="H36" t="n">
-        <v>352.5</v>
+        <v>316.5</v>
       </c>
       <c r="I36" t="n">
         <v>323.9434530382135</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K36" t="n">
-        <v>14</v>
+        <v>2.36</v>
       </c>
       <c r="L36" t="n">
         <v>14.91</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>23.2</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44018</v>
+        <v>44019</v>
       </c>
       <c r="H37" t="n">
-        <v>368.35</v>
+        <v>375.35</v>
       </c>
       <c r="I37" t="n">
         <v>372.0090533489189</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
-        <v>-16.38</v>
+        <v>-18.59</v>
       </c>
       <c r="L37" t="n">
-        <v>16.9</v>
+        <v>19.43</v>
       </c>
       <c r="M37" t="n">
         <v>1.96</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>16.36</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H38" t="n">
-        <v>455.05</v>
+        <v>452.65</v>
       </c>
       <c r="I38" t="n">
         <v>455.0066052151683</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K38" t="n">
-        <v>21.23</v>
+        <v>20.59</v>
       </c>
       <c r="L38" t="n">
         <v>5.91</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>11.09</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44126</v>
+        <v>44127</v>
       </c>
       <c r="H39" t="n">
-        <v>464.1</v>
+        <v>495.1</v>
       </c>
       <c r="I39" t="n">
         <v>491.0895604556171</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.53</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>5.6</v>
+        <v>10.18</v>
       </c>
       <c r="M39" t="n">
         <v>2.21</v>
       </c>
       <c r="N39" t="n">
-        <v>3.89</v>
+        <v>6.68</v>
       </c>
       <c r="O39" t="n">
         <v>-0.53</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.46</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H40" t="n">
-        <v>581</v>
+        <v>570.55</v>
       </c>
       <c r="I40" t="n">
         <v>573.878340666183</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K40" t="n">
-        <v>17.35</v>
+        <v>15.24</v>
       </c>
       <c r="L40" t="n">
         <v>10.12</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>13.07</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44320</v>
+        <v>44321</v>
       </c>
       <c r="H41" t="n">
-        <v>631.8</v>
+        <v>639.7</v>
       </c>
       <c r="I41" t="n">
         <v>634.3874298515123</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.74</v>
+        <v>-12.12</v>
       </c>
       <c r="L41" t="n">
         <v>14.64</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.41</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H42" t="n">
-        <v>775.1</v>
+        <v>750.8</v>
       </c>
       <c r="I42" t="n">
         <v>760.6238799596556</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K42" t="n">
-        <v>21.17</v>
+        <v>17.37</v>
       </c>
       <c r="L42" t="n">
         <v>2.57</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.6</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44481</v>
+        <v>44482</v>
       </c>
       <c r="H43" t="n">
-        <v>790.55</v>
+        <v>804.2</v>
       </c>
       <c r="I43" t="n">
         <v>794.9205261569227</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.29</v>
+        <v>-7.11</v>
       </c>
       <c r="L43" t="n">
         <v>12.52</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.82</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H44" t="n">
-        <v>778.75</v>
+        <v>740.95</v>
       </c>
       <c r="I44" t="n">
         <v>764.5624849420631</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.16</v>
+        <v>-7.86</v>
       </c>
       <c r="L44" t="n">
-        <v>6.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>1.18</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>15.11</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44566</v>
+        <v>44567</v>
       </c>
       <c r="H45" t="n">
-        <v>721</v>
+        <v>748.95</v>
       </c>
       <c r="I45" t="n">
         <v>738.9638692112661</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K45" t="n">
-        <v>2.69</v>
+        <v>-1.08</v>
       </c>
       <c r="L45" t="n">
         <v>5.54</v>
@@ -3006,7 +3545,7 @@
         <v>1.32</v>
       </c>
       <c r="N45" t="n">
-        <v>3.56</v>
+        <v>3.88</v>
       </c>
       <c r="O45" t="n">
         <v>-4.85</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.83</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H46" t="n">
-        <v>740.4</v>
+        <v>718.9</v>
       </c>
       <c r="I46" t="n">
         <v>720.8973396502562</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.14</v>
+        <v>-4.01</v>
       </c>
       <c r="L46" t="n">
-        <v>4.53</v>
+        <v>5.2</v>
       </c>
       <c r="M46" t="n">
         <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="O46" t="n">
         <v>3.88</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44641</v>
+        <v>44642</v>
       </c>
       <c r="H47" t="n">
-        <v>669.05</v>
+        <v>689.5</v>
       </c>
       <c r="I47" t="n">
         <v>688.8429448744604</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K47" t="n">
-        <v>6.93</v>
+        <v>4.09</v>
       </c>
       <c r="L47" t="n">
         <v>6.71</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.78</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44680</v>
+        <v>44683</v>
       </c>
       <c r="H48" t="n">
-        <v>701.75</v>
+        <v>678.45</v>
       </c>
       <c r="I48" t="n">
         <v>680.8180803726673</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>1.78</v>
+        <v>-1.6</v>
       </c>
       <c r="L48" t="n">
         <v>3.12</v>
       </c>
       <c r="M48" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="N48" t="n">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="O48" t="n">
         <v>3.06</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>10.72</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44698</v>
+        <v>44699</v>
       </c>
       <c r="H49" t="n">
-        <v>678.15</v>
+        <v>690.55</v>
       </c>
       <c r="I49" t="n">
         <v>686.3613638681136</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K49" t="n">
-        <v>0.04</v>
+        <v>-1.78</v>
       </c>
       <c r="L49" t="n">
-        <v>2.46</v>
+        <v>3.18</v>
       </c>
       <c r="M49" t="n">
         <v>1.24</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>12.38</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H50" t="n">
-        <v>634.1</v>
+        <v>622.9</v>
       </c>
       <c r="I50" t="n">
         <v>624.3806425856577</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K50" t="n">
-        <v>-8.17</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>9.359999999999999</v>
+        <v>10.94</v>
       </c>
       <c r="M50" t="n">
         <v>1.71</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>11.64</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44763</v>
+        <v>44764</v>
       </c>
       <c r="H51" t="n">
-        <v>688.15</v>
+        <v>706.6</v>
       </c>
       <c r="I51" t="n">
         <v>690.8472908495974</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K51" t="n">
-        <v>-10.48</v>
+        <v>-13.44</v>
       </c>
       <c r="L51" t="n">
-        <v>11.25</v>
+        <v>14.77</v>
       </c>
       <c r="M51" t="n">
         <v>1.83</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.77</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H52" t="n">
-        <v>747.1</v>
+        <v>723.9</v>
       </c>
       <c r="I52" t="n">
         <v>729.9806402884747</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K52" t="n">
-        <v>5.73</v>
+        <v>2.45</v>
       </c>
       <c r="L52" t="n">
         <v>2.21</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>11.33</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44841</v>
+        <v>44844</v>
       </c>
       <c r="H53" t="n">
-        <v>767.35</v>
+        <v>778.15</v>
       </c>
       <c r="I53" t="n">
         <v>769.6319491274437</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>-6</v>
+        <v>-7.49</v>
       </c>
       <c r="L53" t="n">
-        <v>6.78</v>
+        <v>7.94</v>
       </c>
       <c r="M53" t="n">
         <v>2.19</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>12.26</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44883</v>
+        <v>44886</v>
       </c>
       <c r="H54" t="n">
-        <v>836.7</v>
+        <v>826.85</v>
       </c>
       <c r="I54" t="n">
         <v>827.8342172106594</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K54" t="n">
-        <v>7.52</v>
+        <v>6.26</v>
       </c>
       <c r="L54" t="n">
         <v>4.63</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>7.67</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44908</v>
+        <v>44909</v>
       </c>
       <c r="H55" t="n">
-        <v>889.45</v>
+        <v>908.65</v>
       </c>
       <c r="I55" t="n">
         <v>889.8801827296576</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>-7.57</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>9.09</v>
+        <v>10.18</v>
       </c>
       <c r="M55" t="n">
         <v>1.41</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44971</v>
+        <v>44972</v>
       </c>
       <c r="H56" t="n">
-        <v>873.5</v>
+        <v>835.7</v>
       </c>
       <c r="I56" t="n">
         <v>837.828551159968</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.87</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>8.94</v>
+        <v>10.68</v>
       </c>
       <c r="M56" t="n">
-        <v>0.71</v>
+        <v>2.69</v>
       </c>
       <c r="N56" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="O56" t="n">
         <v>2.16</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.93</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45083</v>
+        <v>45084</v>
       </c>
       <c r="H57" t="n">
-        <v>802.5</v>
+        <v>808.45</v>
       </c>
       <c r="I57" t="n">
         <v>802.5357463832858</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K57" t="n">
-        <v>3.97</v>
+        <v>3.26</v>
       </c>
       <c r="L57" t="n">
         <v>4.62</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.66</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H58" t="n">
-        <v>1071.05</v>
+        <v>1056.45</v>
       </c>
       <c r="I58" t="n">
         <v>1062.187339539425</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K58" t="n">
-        <v>32.48</v>
+        <v>30.68</v>
       </c>
       <c r="L58" t="n">
         <v>1.16</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.62</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45251</v>
+        <v>45252</v>
       </c>
       <c r="H59" t="n">
-        <v>1077.75</v>
+        <v>1096.75</v>
       </c>
       <c r="I59" t="n">
         <v>1091.330242937829</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.02</v>
+        <v>-3.81</v>
       </c>
       <c r="L59" t="n">
-        <v>2.72</v>
+        <v>3.97</v>
       </c>
       <c r="M59" t="n">
         <v>1.06</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.31</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H60" t="n">
-        <v>1223.95</v>
+        <v>1193.45</v>
       </c>
       <c r="I60" t="n">
         <v>1195.511721221329</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K60" t="n">
-        <v>11.6</v>
+        <v>8.82</v>
       </c>
       <c r="L60" t="n">
         <v>2.35</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>9.34</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45330</v>
+        <v>45331</v>
       </c>
       <c r="H61" t="n">
-        <v>1282.3</v>
+        <v>1314.05</v>
       </c>
       <c r="I61" t="n">
         <v>1300.963641568801</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.44</v>
+        <v>-10.11</v>
       </c>
       <c r="L61" t="n">
-        <v>9.35</v>
+        <v>10.71</v>
       </c>
       <c r="M61" t="n">
         <v>0.98</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>9.23</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H62" t="n">
-        <v>1314.05</v>
+        <v>1130.95</v>
       </c>
       <c r="I62" t="n">
         <v>1192.797831142709</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>-13.93</v>
       </c>
       <c r="L62" t="n">
-        <v>3.14</v>
+        <v>15</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>13.93</v>
       </c>
       <c r="O62" t="n">
         <v>2.48</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>22.13</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45405</v>
+        <v>45406</v>
       </c>
       <c r="H63" t="n">
-        <v>1206.55</v>
+        <v>1222</v>
       </c>
       <c r="I63" t="n">
         <v>1208.869296968542</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.68</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L63" t="n">
         <v>17.6</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.21</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H64" t="n">
-        <v>1608.25</v>
+        <v>1446.25</v>
       </c>
       <c r="I64" t="n">
         <v>1467.591363158423</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K64" t="n">
-        <v>31.61</v>
+        <v>18.35</v>
       </c>
       <c r="L64" t="n">
         <v>1.06</v>
@@ -4089,7 +4856,7 @@
         <v>0.65</v>
       </c>
       <c r="N64" t="n">
-        <v>2.13</v>
+        <v>10.07</v>
       </c>
       <c r="O64" t="n">
         <v>1.28</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>18.27</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H65" t="n">
-        <v>1636.95</v>
+        <v>1717.3</v>
       </c>
       <c r="I65" t="n">
         <v>1670.505745841678</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K65" t="n">
-        <v>-13.19</v>
+        <v>-18.74</v>
       </c>
       <c r="L65" t="n">
-        <v>14.43</v>
+        <v>20.27</v>
       </c>
       <c r="M65" t="n">
         <v>3.03</v>
       </c>
       <c r="N65" t="n">
-        <v>3.81</v>
+        <v>4.91</v>
       </c>
       <c r="O65" t="n">
         <v>-10.07</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>13.21</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H66" t="n">
-        <v>1621.5</v>
+        <v>1579.4</v>
       </c>
       <c r="I66" t="n">
         <v>1583.275768159064</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K66" t="n">
-        <v>-5.58</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>6.68</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M66" t="n">
         <v>0.46</v>
       </c>
       <c r="N66" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="O66" t="n">
         <v>4.91</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>10.13</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45502</v>
+        <v>45503</v>
       </c>
       <c r="H67" t="n">
-        <v>1737</v>
+        <v>1743.85</v>
       </c>
       <c r="I67" t="n">
         <v>1739.395098390695</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K67" t="n">
-        <v>-9.98</v>
+        <v>-10.41</v>
       </c>
       <c r="L67" t="n">
-        <v>10.61</v>
+        <v>10.99</v>
       </c>
       <c r="M67" t="n">
         <v>0.77</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>10.23</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H68" t="n">
-        <v>1655.4</v>
+        <v>1553.05</v>
       </c>
       <c r="I68" t="n">
         <v>1573.080624480082</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.07</v>
+        <v>-10.94</v>
       </c>
       <c r="L68" t="n">
-        <v>5.5</v>
+        <v>11.8</v>
       </c>
       <c r="M68" t="n">
-        <v>0.61</v>
+        <v>4.56</v>
       </c>
       <c r="N68" t="n">
-        <v>3.62</v>
+        <v>6.18</v>
       </c>
       <c r="O68" t="n">
         <v>0.39</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>13.02</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H69" t="n">
-        <v>1099.95</v>
+        <v>1136</v>
       </c>
       <c r="I69" t="n">
         <v>1120.085627537801</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K69" t="n">
-        <v>29.17</v>
+        <v>26.85</v>
       </c>
       <c r="L69" t="n">
         <v>6.56</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>8</v>
+      </c>
+      <c r="U69" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>11.05</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H70" t="n">
-        <v>1117.1</v>
+        <v>1026.05</v>
       </c>
       <c r="I70" t="n">
         <v>1081.046176158659</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.66</v>
+        <v>-9.68</v>
       </c>
       <c r="L70" t="n">
-        <v>4.71</v>
+        <v>10.74</v>
       </c>
       <c r="M70" t="n">
         <v>1.99</v>
       </c>
       <c r="N70" t="n">
-        <v>3.11</v>
+        <v>8.15</v>
       </c>
       <c r="O70" t="n">
         <v>3.28</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>16.78</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H71" t="n">
-        <v>1094.2</v>
+        <v>1103.6</v>
       </c>
       <c r="I71" t="n">
         <v>1098.633979366582</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.64</v>
+        <v>-7.56</v>
       </c>
       <c r="L71" t="n">
-        <v>7.26</v>
+        <v>8.4</v>
       </c>
       <c r="M71" t="n">
         <v>4.56</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>12.49</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="H72" t="n">
-        <v>1261.5</v>
+        <v>1234.8</v>
       </c>
       <c r="I72" t="n">
         <v>1243.003662929508</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K72" t="n">
-        <v>14.31</v>
+        <v>11.89</v>
       </c>
       <c r="L72" t="n">
         <v>2.14</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H73" t="n">
-        <v>1199.9</v>
+        <v>1211.9</v>
       </c>
       <c r="I73" t="n">
         <v>1208.647772784046</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K73" t="n">
-        <v>2.83</v>
+        <v>1.85</v>
       </c>
       <c r="L73" t="n">
         <v>2.59</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,25 +5525,25 @@
         <v>9.17</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H74" t="n">
-        <v>1207.3</v>
+        <v>1181.1</v>
       </c>
       <c r="I74" t="n">
         <v>1186.66992595039</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.38</v>
+        <v>-2.54</v>
       </c>
       <c r="L74" t="n">
-        <v>1.48</v>
+        <v>2.71</v>
       </c>
       <c r="M74" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N74" t="n">
         <v>3.36</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H75" t="n">
-        <v>1243.4</v>
+        <v>1300.1</v>
       </c>
       <c r="I75" t="n">
         <v>1279.799405532999</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K75" t="n">
-        <v>-5.27</v>
+        <v>-10.08</v>
       </c>
       <c r="L75" t="n">
-        <v>8.029999999999999</v>
+        <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>0.99</v>
+        <v>2.05</v>
       </c>
       <c r="N75" t="n">
-        <v>2.79</v>
+        <v>4.56</v>
       </c>
       <c r="O75" t="n">
         <v>-2.17</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H76" t="n">
-        <v>1415.1</v>
+        <v>1394.1</v>
       </c>
       <c r="I76" t="n">
         <v>1402.41866586204</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K76" t="n">
-        <v>8.85</v>
+        <v>7.23</v>
       </c>
       <c r="L76" t="n">
         <v>2.7</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>7.29</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H77" t="n">
-        <v>1443.7</v>
+        <v>1539</v>
       </c>
       <c r="I77" t="n">
         <v>1482.072879812466</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K77" t="n">
-        <v>-3.56</v>
+        <v>-10.39</v>
       </c>
       <c r="L77" t="n">
-        <v>5.8</v>
+        <v>13.91</v>
       </c>
       <c r="M77" t="n">
-        <v>1.36</v>
+        <v>8.06</v>
       </c>
       <c r="N77" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="O77" t="n">
         <v>-1.48</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>10.57</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H78" t="n">
-        <v>1779.6</v>
+        <v>1675.1</v>
       </c>
       <c r="I78" t="n">
         <v>1761.006691691364</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K78" t="n">
-        <v>15.63</v>
+        <v>8.84</v>
       </c>
       <c r="L78" t="n">
         <v>0.65</v>
@@ -4887,7 +5822,7 @@
         <v>2.67</v>
       </c>
       <c r="N78" t="n">
-        <v>3.2</v>
+        <v>5.87</v>
       </c>
       <c r="O78" t="n">
         <v>6.6</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>15.16</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H79" t="n">
-        <v>1831.6</v>
+        <v>1855.8</v>
       </c>
       <c r="I79" t="n">
         <v>1834.229612565882</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K79" t="n">
-        <v>-9.34</v>
+        <v>-10.79</v>
       </c>
       <c r="L79" t="n">
-        <v>10.4</v>
+        <v>11.04</v>
       </c>
       <c r="M79" t="n">
         <v>3.12</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>11.05</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H80" t="n">
-        <v>2093.1</v>
+        <v>2051</v>
       </c>
       <c r="I80" t="n">
         <v>2080.62969736587</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K80" t="n">
-        <v>12.79</v>
+        <v>10.52</v>
       </c>
       <c r="L80" t="n">
         <v>2.02</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>5</v>
+      </c>
+      <c r="U80" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>54</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.9</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -10079,7 +11058,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -10089,7 +11068,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -10099,7 +11078,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="14">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.57</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.56</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.5</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.6</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.77</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.56</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="21">
@@ -10179,7 +11158,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.6</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="22">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="25">
@@ -10219,7 +11198,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.61</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="26">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.4</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="27">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
